--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-1.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-1.xlsx
@@ -1,42 +1,475 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\NEW-RULE\positive\01\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8B3127-39F9-4BE6-B4DE-954CB6B2A80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="dm.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="143">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>ts.xpt</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameters</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>TSSEQ</t>
+  </si>
+  <si>
+    <t>TSGRPID</t>
+  </si>
+  <si>
+    <t>TSPARMCD</t>
+  </si>
+  <si>
+    <t>TSPARM</t>
+  </si>
+  <si>
+    <t>TSVAL</t>
+  </si>
+  <si>
+    <t>TSVALNF</t>
+  </si>
+  <si>
+    <t>TSVALCD</t>
+  </si>
+  <si>
+    <t>TSVCDREF</t>
+  </si>
+  <si>
+    <t>TSVCDVER</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Group ID</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Short Name</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter</t>
+  </si>
+  <si>
+    <t>Parameter Value</t>
+  </si>
+  <si>
+    <t>Parameter Null Flavor</t>
+  </si>
+  <si>
+    <t>Parameter Value Code</t>
+  </si>
+  <si>
+    <t>Name of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Version of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CDISC</t>
+  </si>
+  <si>
+    <t>2018-12-21</t>
+  </si>
+  <si>
+    <t>dm.xpt</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>SSDTC</t>
+  </si>
+  <si>
+    <t>2018-04-15</t>
+  </si>
+  <si>
+    <t>Study Start Date</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>SUBJID</t>
+  </si>
+  <si>
+    <t>RFSTDTC</t>
+  </si>
+  <si>
+    <t>RFENDTC</t>
+  </si>
+  <si>
+    <t>RFXSTDTC</t>
+  </si>
+  <si>
+    <t>RFXENDTC</t>
+  </si>
+  <si>
+    <t>RFICDTC</t>
+  </si>
+  <si>
+    <t>RFPENDTC</t>
+  </si>
+  <si>
+    <t>DTHDTC</t>
+  </si>
+  <si>
+    <t>DTHFL</t>
+  </si>
+  <si>
+    <t>SITEID</t>
+  </si>
+  <si>
+    <t>BRTHDTC</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>AGEU</t>
+  </si>
+  <si>
+    <t>SEX</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>ETHNIC</t>
+  </si>
+  <si>
+    <t>ARMCD</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
+    <t>ACTARMCD</t>
+  </si>
+  <si>
+    <t>ACTARM</t>
+  </si>
+  <si>
+    <t>ARMNRS</t>
+  </si>
+  <si>
+    <t>ACTARMUD</t>
+  </si>
+  <si>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Subject Identifier for the Study</t>
+  </si>
+  <si>
+    <t>Subject Reference Start Date/Time</t>
+  </si>
+  <si>
+    <t>Subject Reference End Date/Time</t>
+  </si>
+  <si>
+    <t>Date/Time of First Study Treatment</t>
+  </si>
+  <si>
+    <t>Date/Time of Last Study Treatment</t>
+  </si>
+  <si>
+    <t>Date/Time of Informed Consent</t>
+  </si>
+  <si>
+    <t>Date/Time of End of Participation</t>
+  </si>
+  <si>
+    <t>Date/Time of Death</t>
+  </si>
+  <si>
+    <t>Subject Death Flag</t>
+  </si>
+  <si>
+    <t>Study Site Identifier</t>
+  </si>
+  <si>
+    <t>Date/Time of Birth</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Age Units</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Race</t>
+  </si>
+  <si>
+    <t>Ethnicity</t>
+  </si>
+  <si>
+    <t>Planned Arm Code</t>
+  </si>
+  <si>
+    <t>Description of Planned Arm</t>
+  </si>
+  <si>
+    <t>Actual Arm Code</t>
+  </si>
+  <si>
+    <t>Description of Actual Arm</t>
+  </si>
+  <si>
+    <t>Reason Arm and/or Actual Arm is Null</t>
+  </si>
+  <si>
+    <t>Description of Unplanned Actual Arm</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>CDISCCORE01</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>015246-099-0000-00000</t>
+  </si>
+  <si>
+    <t>099000000000</t>
+  </si>
+  <si>
+    <t>2018-04-16</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>0990000</t>
+  </si>
+  <si>
+    <t>1940-08-14</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>YEARS</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>NOT HISPANIC OR LATINO</t>
+  </si>
+  <si>
+    <t>IKd</t>
+  </si>
+  <si>
+    <t>ASSIGNED, NOT TREATED</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>015246-099-0000-00001</t>
+  </si>
+  <si>
+    <t>099000000001</t>
+  </si>
+  <si>
+    <t>2018-05-20</t>
+  </si>
+  <si>
+    <t>2018-06-10</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>1941-08-14</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>IKD</t>
+  </si>
+  <si>
+    <t>NOT ASSIGNED</t>
+  </si>
+  <si>
+    <t>015246-099-0000-00002</t>
+  </si>
+  <si>
+    <t>099000000002</t>
+  </si>
+  <si>
+    <t>1942-08-14</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>BLACK OR
+AFRICAN
+AMERICAN</t>
+  </si>
+  <si>
+    <t>SCREEN FAILURE</t>
+  </si>
+  <si>
+    <t>015246-099-0000-00003</t>
+  </si>
+  <si>
+    <t>099000000003</t>
+  </si>
+  <si>
+    <t>2018-05-08T11:20</t>
+  </si>
+  <si>
+    <t>2018-08-29T10:35</t>
+  </si>
+  <si>
+    <t>2018-04-17</t>
+  </si>
+  <si>
+    <t>2018-09-04</t>
+  </si>
+  <si>
+    <t>1947-12-23</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>PLACEBO</t>
+  </si>
+  <si>
+    <t>Placebo</t>
+  </si>
+  <si>
+    <t>UNPLANNED TREATMENT</t>
+  </si>
+  <si>
+    <t>GRC</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0;[Red]0"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -45,55 +478,52 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -102,31 +532,82 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -451,241 +932,849 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>3-4</v>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>Trial Summary Parameters</v>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>TSSEQ</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>TSGRPID</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v>TSPARM</v>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="H1" s="3" t="str">
-        <v>TSVALNF</v>
-      </c>
-      <c r="I1" s="3" t="str">
-        <v>TSVALCD</v>
-      </c>
-      <c r="J1" s="3" t="str">
-        <v>TSVCDREF</v>
-      </c>
-      <c r="K1" s="3" t="str">
-        <v>TSVCDVER</v>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="6" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="6" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="D2" s="6" t="str">
-        <v>Group ID</v>
-      </c>
-      <c r="E2" s="6" t="str">
-        <v>Trial Summary Parameter Short Name</v>
-      </c>
-      <c r="F2" s="6" t="str">
-        <v>Trial Summary Parameter</v>
-      </c>
-      <c r="G2" s="6" t="str">
-        <v>Parameter Value</v>
-      </c>
-      <c r="H2" s="6" t="str">
-        <v>Parameter Null Flavor</v>
-      </c>
-      <c r="I2" s="6" t="str">
-        <v>Parameter Value Code</v>
-      </c>
-      <c r="J2" s="6" t="str">
-        <v>Name of the Reference Terminology</v>
-      </c>
-      <c r="K2" s="6" t="str">
-        <v>Version of the Reference Terminology</v>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Num</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
-        <v>Char</v>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6" t="str">
-        <v>10</v>
-      </c>
-      <c r="B4" s="6" t="str">
-        <v>2</v>
-      </c>
-      <c r="C4" s="6" t="str">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="str">
-        <v>5</v>
-      </c>
-      <c r="E4" s="6" t="str">
-        <v>8</v>
-      </c>
-      <c r="F4" s="6" t="str">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="6" t="str">
-        <v>149</v>
-      </c>
-      <c r="H4" s="6" t="str">
-        <v>2</v>
-      </c>
-      <c r="I4" s="6" t="str">
-        <v>11</v>
-      </c>
-      <c r="J4" s="6" t="str">
-        <v>18</v>
-      </c>
-      <c r="K4" s="6" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="7" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C5" s="7" t="str">
-        <v>1</v>
-      </c>
-      <c r="D5" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E5" s="7" t="str">
-        <v>AGEMIN</v>
-      </c>
-      <c r="F5" s="7" t="str">
-        <v>Minimum Age</v>
-      </c>
-      <c r="G5" s="7">
-        <v>18</v>
-      </c>
-      <c r="H5" s="7" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="7" t="str">
-        <v/>
-      </c>
-      <c r="J5" s="7" t="str">
-        <v>CDISC</v>
-      </c>
-      <c r="K5" s="7" t="str">
-        <v>2018-12-21</v>
+      <c r="B5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError sqref="A1:K4 A5:D5 H5:K5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10521100-C481-40B4-95F5-06F7F9F64B06}">
+  <dimension ref="A1:Z8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>12</v>
+      </c>
+      <c r="B4" s="9">
+        <v>2</v>
+      </c>
+      <c r="C4" s="11">
+        <v>20</v>
+      </c>
+      <c r="D4" s="11">
+        <v>12</v>
+      </c>
+      <c r="E4" s="9">
+        <v>10</v>
+      </c>
+      <c r="F4" s="9">
+        <v>10</v>
+      </c>
+      <c r="G4" s="9">
+        <v>10</v>
+      </c>
+      <c r="H4" s="9">
+        <v>10</v>
+      </c>
+      <c r="I4" s="9">
+        <v>10</v>
+      </c>
+      <c r="J4" s="9">
+        <v>10</v>
+      </c>
+      <c r="K4" s="9">
+        <v>10</v>
+      </c>
+      <c r="L4" s="9">
+        <v>1</v>
+      </c>
+      <c r="M4" s="9">
+        <v>3</v>
+      </c>
+      <c r="N4" s="9">
+        <v>10</v>
+      </c>
+      <c r="O4" s="9">
+        <v>8</v>
+      </c>
+      <c r="P4" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>1</v>
+      </c>
+      <c r="R4" s="9">
+        <v>41</v>
+      </c>
+      <c r="S4" s="9">
+        <v>22</v>
+      </c>
+      <c r="T4" s="9">
+        <v>8</v>
+      </c>
+      <c r="U4" s="9">
+        <v>28</v>
+      </c>
+      <c r="V4" s="9">
+        <v>8</v>
+      </c>
+      <c r="W4" s="9">
+        <v>28</v>
+      </c>
+      <c r="X4" s="9">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>200</v>
+      </c>
+      <c r="Z4" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="S6" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="X6" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="S7" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q8" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="T8" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="U8" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="V8" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="W8" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="X8" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-1.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-1.xlsx
@@ -1,42 +1,202 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\NEW-RULE\positive\01\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941CBA60-4671-4A11-9123-72B5A164BCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="54">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>ts.xpt</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameters</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>TSSEQ</t>
+  </si>
+  <si>
+    <t>TSGRPID</t>
+  </si>
+  <si>
+    <t>TSPARMCD</t>
+  </si>
+  <si>
+    <t>TSPARM</t>
+  </si>
+  <si>
+    <t>TSVAL</t>
+  </si>
+  <si>
+    <t>TSVALNF</t>
+  </si>
+  <si>
+    <t>TSVALCD</t>
+  </si>
+  <si>
+    <t>TSVCDREF</t>
+  </si>
+  <si>
+    <t>TSVCDVER</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Group ID</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Short Name</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter</t>
+  </si>
+  <si>
+    <t>Parameter Value</t>
+  </si>
+  <si>
+    <t>Parameter Null Flavor</t>
+  </si>
+  <si>
+    <t>Parameter Value Code</t>
+  </si>
+  <si>
+    <t>Name of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Version of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2018-12-21</t>
+  </si>
+  <si>
+    <t>COMPTRT</t>
+  </si>
+  <si>
+    <t>Additional</t>
+  </si>
+  <si>
+    <t>Val 1</t>
+  </si>
+  <si>
+    <t>TRT</t>
+  </si>
+  <si>
+    <t>Val 2</t>
+  </si>
+  <si>
+    <t>CURTRT</t>
+  </si>
+  <si>
+    <t>Current Treatment</t>
+  </si>
+  <si>
+    <t>DRUG A1</t>
+  </si>
+  <si>
+    <t>UNII</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -45,62 +205,40 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -109,24 +247,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -451,241 +597,343 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>3-4</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>Trial Summary Parameters</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>TSSEQ</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>TSGRPID</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v>TSPARM</v>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="H1" s="3" t="str">
-        <v>TSVALNF</v>
-      </c>
-      <c r="I1" s="3" t="str">
-        <v>TSVALCD</v>
-      </c>
-      <c r="J1" s="3" t="str">
-        <v>TSVCDREF</v>
-      </c>
-      <c r="K1" s="3" t="str">
-        <v>TSVCDVER</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="6" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="6" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="D2" s="6" t="str">
-        <v>Group ID</v>
-      </c>
-      <c r="E2" s="6" t="str">
-        <v>Trial Summary Parameter Short Name</v>
-      </c>
-      <c r="F2" s="6" t="str">
-        <v>Trial Summary Parameter</v>
-      </c>
-      <c r="G2" s="6" t="str">
-        <v>Parameter Value</v>
-      </c>
-      <c r="H2" s="6" t="str">
-        <v>Parameter Null Flavor</v>
-      </c>
-      <c r="I2" s="6" t="str">
-        <v>Parameter Value Code</v>
-      </c>
-      <c r="J2" s="6" t="str">
-        <v>Name of the Reference Terminology</v>
-      </c>
-      <c r="K2" s="6" t="str">
-        <v>Version of the Reference Terminology</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Num</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="str">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6" t="str">
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="str">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="str">
-        <v>5</v>
-      </c>
-      <c r="E4" s="6" t="str">
-        <v>8</v>
-      </c>
-      <c r="F4" s="6" t="str">
+      <c r="E6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="6" t="str">
-        <v>149</v>
-      </c>
-      <c r="H4" s="6" t="str">
-        <v>2</v>
-      </c>
-      <c r="I4" s="6" t="str">
-        <v>11</v>
-      </c>
-      <c r="J4" s="6" t="str">
-        <v>18</v>
-      </c>
-      <c r="K4" s="6" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="7" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C5" s="7" t="str">
-        <v>1</v>
-      </c>
-      <c r="D5" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E5" s="7" t="str">
-        <v>AGEMIN</v>
-      </c>
-      <c r="F5" s="7" t="str">
-        <v>Minimum Age</v>
-      </c>
-      <c r="G5" s="7">
-        <v>18</v>
-      </c>
-      <c r="H5" s="7" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="7" t="str">
-        <v/>
-      </c>
-      <c r="J5" s="7" t="str">
-        <v>CDISC</v>
-      </c>
-      <c r="K5" s="7" t="str">
-        <v>2018-12-21</v>
+      <c r="B7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError sqref="A1:K4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>